--- a/experiment/DAT_bestx4/Test/results-Set5/Set5.xlsx
+++ b/experiment/DAT_bestx4/Test/results-Set5/Set5.xlsx
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34.88</v>
+        <v>34.96</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9415</v>
+        <v>0.9423</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28.72</v>
+        <v>28.85</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9179</v>
+        <v>0.9196</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32.97</v>
+        <v>32.98</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7971</v>
+        <v>0.7974</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30.72</v>
+        <v>30.79</v>
       </c>
       <c r="C6" t="n">
-        <v>0.913</v>
+        <v>0.9136</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32.2</v>
+        <v>32.26</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8925999999999999</v>
+        <v>0.8933</v>
       </c>
     </row>
   </sheetData>
